--- a/artfynd/A 31238-2026 artfynd.xlsx
+++ b/artfynd/A 31238-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AZ133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573411</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573414</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573415</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573416</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573418</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573499</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2022,6 +2082,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573500</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2148,6 +2213,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573501</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2279,6 +2349,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573502</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573503</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2531,6 +2611,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573504</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2657,6 +2742,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573505</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2788,6 +2878,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573506</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2914,6 +3009,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573507</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3035,6 +3135,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573509</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3161,6 +3266,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573510</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3267,6 +3377,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573387</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3378,6 +3493,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573388</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3489,6 +3609,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573389</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3600,6 +3725,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573390</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3735,6 +3865,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573355</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3870,6 +4005,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573356</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4005,6 +4145,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573358</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4140,6 +4285,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573359</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4275,6 +4425,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573360</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4390,6 +4545,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573361</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4525,6 +4685,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4660,6 +4825,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573364</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4795,6 +4965,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573366</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4930,6 +5105,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573367</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5057,6 +5237,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573404</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5179,6 +5364,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573406</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5302,6 +5492,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573370</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5425,6 +5620,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573371</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5548,6 +5748,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573372</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5676,6 +5881,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573369</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5792,6 +6002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573394</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5903,6 +6118,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573396</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6014,6 +6234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573397</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6125,6 +6350,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573398</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6236,6 +6466,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573399</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6347,6 +6582,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573400</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6458,6 +6698,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573401</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6569,6 +6814,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573402</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6685,6 +6935,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573403</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6813,6 +7068,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573420</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6941,6 +7201,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573421</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7069,6 +7334,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573422</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7197,6 +7467,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573423</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7325,6 +7600,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573424</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7453,6 +7733,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573425</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7581,6 +7866,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573426</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7709,6 +7999,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573427</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7837,6 +8132,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573428</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7965,6 +8265,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573429</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8093,6 +8398,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573430</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8221,6 +8531,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573432</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8349,6 +8664,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573434</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8477,6 +8797,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573435</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8605,6 +8930,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573438</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8733,6 +9063,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573440</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8861,6 +9196,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573441</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8989,6 +9329,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573443</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9117,6 +9462,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573444</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9245,6 +9595,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573447</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9364,6 +9719,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573449</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9492,6 +9852,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573450</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9620,6 +9985,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573451</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9748,6 +10118,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573452</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9876,6 +10251,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573453</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10004,6 +10384,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573455</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10132,6 +10517,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573456</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10260,6 +10650,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573457</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10388,6 +10783,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573458</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10516,6 +10916,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573459</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10644,6 +11049,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573461</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10772,6 +11182,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573462</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10900,6 +11315,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573464</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11028,6 +11448,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573465</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11156,6 +11581,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573466</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11284,6 +11714,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573467</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11412,6 +11847,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573468</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11540,6 +11980,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573469</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11668,6 +12113,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573471</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11796,6 +12246,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573472</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11924,6 +12379,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573474</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12052,6 +12512,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573475</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12180,6 +12645,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573477</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12308,6 +12778,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573478</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12436,6 +12911,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573479</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12564,6 +13044,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573480</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12692,6 +13177,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573481</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12820,6 +13310,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573482</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12948,6 +13443,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573485</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13076,6 +13576,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573487</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13200,6 +13705,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573488</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13328,6 +13838,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573489</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13440,6 +13955,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573379</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13547,6 +14067,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573380</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13654,6 +14179,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573381</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13761,6 +14291,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573383</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13868,6 +14403,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573384</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13980,6 +14520,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573386</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -14091,6 +14636,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573516</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14202,6 +14752,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573517</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14313,6 +14868,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573518</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14424,6 +14984,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573520</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14535,6 +15100,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573521</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14646,6 +15216,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573522</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14757,6 +15332,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573523</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14868,6 +15448,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573524</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14979,6 +15564,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573526</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15090,6 +15680,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573528</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15201,6 +15796,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573529</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15312,6 +15912,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573530</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15423,6 +16028,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573531</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15534,6 +16144,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573532</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15645,6 +16260,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573533</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15761,6 +16381,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573534</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15872,6 +16497,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573391</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15983,6 +16613,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573392</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16094,6 +16729,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573393</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16205,6 +16845,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573494</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16316,6 +16961,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573496</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16422,6 +17072,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573498</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16528,6 +17183,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573511</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16639,8 +17299,147 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132573512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>